--- a/assets/schedule.xlsx
+++ b/assets/schedule.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Full" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t xml:space="preserve">Course
 Week</t>
@@ -61,7 +61,7 @@
     <t xml:space="preserve">A1 Peer-Review</t>
   </si>
   <si>
-    <t xml:space="preserve">A1: 2025-10-05 @ 23:59</t>
+    <t xml:space="preserve">A1: 2026-10-09 @ 23:59</t>
   </si>
   <si>
     <t xml:space="preserve">CFA II</t>
@@ -74,12 +74,6 @@
   </si>
   <si>
     <t xml:space="preserve">Multiple group models</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A3 Peer-Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A3: 2025-11-02 @ 23:59</t>
   </si>
 </sst>
 </file>
@@ -448,9 +442,6 @@
       <c r="C10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -461,9 +452,6 @@
       </c>
       <c r="C11" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
